--- a/store/May-2026/Mail Attachment/LinkedIn_Report_31-May-2026.xlsx
+++ b/store/May-2026/Mail Attachment/LinkedIn_Report_31-May-2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,324 +484,6 @@
           <t>Correct Cost Code</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>WTI-20260530-3905548</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GRISBIN JOBINSON KOLLANNUR</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-30 19:00:00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>9846718980</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>grisbin@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Kochi</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>WTI-20260530-3905417</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MR.ANKIT JAIN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-31 11:00:00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>7574842024</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ajain5@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Dehradun</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2418</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WTI-20260530-3905565</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PALLAVI KAR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-31 11:30:00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>9650254463</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>pkar@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WTI-20260530-3905295</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SANTOSH KRISHNAMOORTHY</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-31 13:30:00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>9810399434</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>sankrishnamoorthy@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2501</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WTI-20260531-3905857</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ANIRUDH DUREHA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-31 19:30:00</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>9899233705</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>adureha@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2180</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WTI-20260530-3905297</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MRS.SHERIN RACHEL JACOB</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-31 20:30:00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>9916999792</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>shjacob@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>5114</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
